--- a/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
+++ b/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\TTLE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\TTLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CC5EDA-16E8-45C6-851B-8000B937503F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38156F0C-A178-4103-B28F-F0C9E7C7D60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31365" yWindow="2355" windowWidth="21585" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
-    <sheet name="A54.tranSubsector_logit_revised" sheetId="11" r:id="rId2"/>
-    <sheet name="TTLE" sheetId="10" r:id="rId3"/>
+    <sheet name="TTLE" sheetId="10" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>ships</t>
   </si>
@@ -68,6 +67,9 @@
     <t>Logit exponent</t>
   </si>
   <si>
+    <t>None needed.  Handled through calibration.</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -86,157 +88,10 @@
     <t>data on technology buyers' behavior.</t>
   </si>
   <si>
+    <t>For more on this, see the "Modified Logit" equation description at:</t>
+  </si>
+  <si>
     <t>https://jgcri.github.io/gcam-doc/choice.html</t>
-  </si>
-  <si>
-    <t>Calibration</t>
-  </si>
-  <si>
-    <t># File: A54.tranSubsector_logit_revised.csv</t>
-  </si>
-  <si>
-    <t># Title: Transportation default subsector logit exponents</t>
-  </si>
-  <si>
-    <t># Source: Documented in JIRA issue https://jira.pnnl.gov/jira/browse/JGCRI-358?src=confmacro.</t>
-  </si>
-  <si>
-    <t># Units: Unitless</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Column types: ccicc </t>
-  </si>
-  <si>
-    <t># ----------</t>
-  </si>
-  <si>
-    <t>supplysector</t>
-  </si>
-  <si>
-    <t>tranSubsector</t>
-  </si>
-  <si>
-    <t>logit.exponent</t>
-  </si>
-  <si>
-    <t>logit.factor</t>
-  </si>
-  <si>
-    <t>logit.type</t>
-  </si>
-  <si>
-    <t>trn_aviation_intl</t>
-  </si>
-  <si>
-    <t>International Aviation</t>
-  </si>
-  <si>
-    <t>absolute-cost-logit</t>
-  </si>
-  <si>
-    <t>trn_freight</t>
-  </si>
-  <si>
-    <t>Domestic Ship</t>
-  </si>
-  <si>
-    <t>Freight Rail</t>
-  </si>
-  <si>
-    <t>Fuel types and efficiency levels</t>
-  </si>
-  <si>
-    <t>trn_freight_road</t>
-  </si>
-  <si>
-    <t>Light truck</t>
-  </si>
-  <si>
-    <t>Fuel types</t>
-  </si>
-  <si>
-    <t>Medium truck</t>
-  </si>
-  <si>
-    <t>Heavy truck</t>
-  </si>
-  <si>
-    <t>trn_pass</t>
-  </si>
-  <si>
-    <t>Cycle</t>
-  </si>
-  <si>
-    <t>Domestic Aviation</t>
-  </si>
-  <si>
-    <t>HSR</t>
-  </si>
-  <si>
-    <t>Passenger Rail</t>
-  </si>
-  <si>
-    <t>Walk</t>
-  </si>
-  <si>
-    <t>trn_pass_road</t>
-  </si>
-  <si>
-    <t>Bus</t>
-  </si>
-  <si>
-    <t>trn_pass_road_LDV</t>
-  </si>
-  <si>
-    <t>2W and 3W</t>
-  </si>
-  <si>
-    <t>trn_pass_road_LDV_4W</t>
-  </si>
-  <si>
-    <t>Car</t>
-  </si>
-  <si>
-    <t>Fuel types and ICE efficiency levels</t>
-  </si>
-  <si>
-    <t>Large Car and Truck</t>
-  </si>
-  <si>
-    <t>Mini Car</t>
-  </si>
-  <si>
-    <t>trn_shipping_intl</t>
-  </si>
-  <si>
-    <t>International Ship</t>
-  </si>
-  <si>
-    <t># Passthrough tranSubsectors are listed belowabsolute-cost-logit</t>
-  </si>
-  <si>
-    <t>road</t>
-  </si>
-  <si>
-    <t>LDV</t>
-  </si>
-  <si>
-    <t>bus</t>
-  </si>
-  <si>
-    <t>4W</t>
-  </si>
-  <si>
-    <t>2W</t>
-  </si>
-  <si>
-    <t>For non-road we use -0.1 because of costs preventing the model from solving.</t>
-  </si>
-  <si>
-    <t>We use calibrated values in onroad sectors.</t>
-  </si>
-  <si>
-    <t>For more on this, see the "Unmodified Logit" equation description at:</t>
   </si>
 </sst>
 </file>
@@ -247,7 +102,7 @@
     <numFmt numFmtId="164" formatCode="###0.00_)"/>
     <numFmt numFmtId="165" formatCode="#,##0_)"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -912,15 +767,18 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="60">
     <cellStyle name="20% - Accent1" xfId="33" builtinId="30" customBuiltin="1"/>
@@ -1028,9 +886,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1068,9 +926,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1103,9 +961,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1138,9 +1013,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1314,77 +1206,214 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B54"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B62"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="45.42578125" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B38" s="2"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B41" s="2"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B42" s="2"/>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B43" s="2"/>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B47" s="2"/>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B48" s="2"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="2"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B50" s="2"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="1"/>
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B52" s="2"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B53" s="2"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B54" s="2"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B55" s="2"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B56" s="2"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B57" s="2"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B58" s="2"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B59" s="2"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B60" s="2"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B61" s="2"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B62" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1393,417 +1422,93 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97FB3F6-A063-4685-A6D1-3D6F2007ED8F}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2">
+        <v>-3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4">
+        <v>-3</v>
+      </c>
+      <c r="C3" s="4">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4">
+        <v>-3</v>
+      </c>
+      <c r="C4" s="4">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4">
+        <v>-3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4">
+        <v>-3</v>
+      </c>
+      <c r="C6" s="4">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8">
-        <v>-6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9">
-        <v>-6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10">
-        <v>-1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11">
-        <v>-8</v>
-      </c>
-      <c r="D11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12">
-        <v>-8</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13">
-        <v>-8</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14">
-        <v>-6</v>
-      </c>
-      <c r="E14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15">
-        <v>-6</v>
-      </c>
-      <c r="E15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16">
-        <v>-6</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17">
-        <v>-1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18">
-        <v>-6</v>
-      </c>
-      <c r="E18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
         <v>-3</v>
       </c>
-      <c r="D19" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20">
-        <v>-8</v>
-      </c>
-      <c r="D20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21">
-        <v>-8</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22">
-        <v>-8</v>
-      </c>
-      <c r="D22" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23">
-        <v>-8</v>
-      </c>
-      <c r="D23" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24">
-        <v>-6</v>
-      </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26">
-        <v>-6</v>
-      </c>
-      <c r="E26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27">
-        <v>-6</v>
-      </c>
-      <c r="E27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28">
-        <v>-6</v>
-      </c>
-      <c r="E28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29">
-        <v>-6</v>
-      </c>
-      <c r="E29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30">
-        <v>-6</v>
-      </c>
-      <c r="E30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31">
-        <v>-6</v>
-      </c>
-      <c r="E31" t="s">
-        <v>32</v>
+      <c r="C7" s="4">
+        <v>-3</v>
       </c>
     </row>
   </sheetData>
@@ -1811,97 +1516,173 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>-80</v>
-      </c>
-      <c r="C2">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>-30</v>
-      </c>
-      <c r="C3">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>-0.1</v>
-      </c>
-      <c r="C4">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>-0.15</v>
-      </c>
-      <c r="C5">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6">
-        <v>-0.1</v>
-      </c>
-      <c r="C6">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>-40</v>
-      </c>
-      <c r="C7">
-        <v>-40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF47025-38FC-4D4C-A172-57EF19919DA6}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF0E423-9D38-426D-8974-49181EF85CAD}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE2417C-9996-4510-9140-E726E730908D}"/>
 </file>
--- a/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
+++ b/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\TTLE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\TTLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38156F0C-A178-4103-B28F-F0C9E7C7D60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60338155-4D1D-4A3C-91F5-32B7D8C9F62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="855" yWindow="1830" windowWidth="26040" windowHeight="14730" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -767,18 +767,15 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="60">
     <cellStyle name="20% - Accent1" xfId="33" builtinId="30" customBuiltin="1"/>
@@ -886,9 +883,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -926,9 +923,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -961,26 +958,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1013,26 +993,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1206,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="45.453125" customWidth="1"/>
@@ -1221,199 +1184,52 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="2"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B30" s="2"/>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B36" s="2"/>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B37" s="2"/>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B38" s="2"/>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B39" s="2"/>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B40" s="2"/>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B41" s="2"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B42" s="2"/>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B43" s="2"/>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B44" s="2"/>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B45" s="2"/>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B46" s="2"/>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B47" s="2"/>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B48" s="2"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B49" s="2"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B50" s="2"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="1"/>
-      <c r="B51" s="2"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B52" s="2"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B53" s="2"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B54" s="2"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B56" s="2"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B57" s="2"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B58" s="2"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B59" s="2"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B60" s="2"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B61" s="2"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B62" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1435,13 +1251,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1449,10 +1265,10 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2">
-        <v>-3</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="B2">
+        <v>-17.27</v>
+      </c>
+      <c r="C2">
         <v>-3</v>
       </c>
     </row>
@@ -1460,10 +1276,10 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>-3</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3">
         <v>-3</v>
       </c>
     </row>
@@ -1471,10 +1287,10 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>-3</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>-3</v>
       </c>
     </row>
@@ -1482,10 +1298,10 @@
       <c r="A5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>-3</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>-3</v>
       </c>
     </row>
@@ -1493,10 +1309,10 @@
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>-3</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>-3</v>
       </c>
     </row>
@@ -1504,10 +1320,10 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>-3</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>-3</v>
       </c>
     </row>
@@ -1517,6 +1333,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1660,7 +1482,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1669,20 +1491,37 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF47025-38FC-4D4C-A172-57EF19919DA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE2417C-9996-4510-9140-E726E730908D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF0E423-9D38-426D-8974-49181EF85CAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF47025-38FC-4D4C-A172-57EF19919DA6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE2417C-9996-4510-9140-E726E730908D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF0E423-9D38-426D-8974-49181EF85CAD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
+++ b/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\TTLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60338155-4D1D-4A3C-91F5-32B7D8C9F62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C493D1C-A248-4271-B070-6073FCB4878E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="855" yWindow="1830" windowWidth="26040" windowHeight="14730" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -1170,17 +1170,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="45.453125" customWidth="1"/>
+    <col min="2" max="2" width="45.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1188,47 +1188,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
     </row>
   </sheetData>
@@ -1243,14 +1243,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -1261,18 +1261,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>-17.27</v>
+        <v>-13</v>
       </c>
       <c r="C2">
         <v>-3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1339,6 +1339,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1482,15 +1491,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE2417C-9996-4510-9140-E726E730908D}">
   <ds:schemaRefs>
@@ -1501,6 +1501,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF0E423-9D38-426D-8974-49181EF85CAD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF47025-38FC-4D4C-A172-57EF19919DA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1516,12 +1524,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF0E423-9D38-426D-8974-49181EF85CAD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
+++ b/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\TTLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C493D1C-A248-4271-B070-6073FCB4878E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D569C0-F6BB-4E65-A4C9-AEF16BBB46F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="1950" windowWidth="27045" windowHeight="14955" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -1299,10 +1299,10 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>-3</v>
+        <v>-0.1</v>
       </c>
       <c r="C5">
-        <v>-3</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1339,15 +1339,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1491,6 +1482,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE2417C-9996-4510-9140-E726E730908D}">
   <ds:schemaRefs>
@@ -1501,14 +1501,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF0E423-9D38-426D-8974-49181EF85CAD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF47025-38FC-4D4C-A172-57EF19919DA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1524,4 +1516,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF0E423-9D38-426D-8974-49181EF85CAD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
+++ b/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\TTLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D569C0-F6BB-4E65-A4C9-AEF16BBB46F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166235BA-B9A1-474C-A7BC-45EBD99E9D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="1950" windowWidth="27045" windowHeight="14955" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25860" yWindow="1755" windowWidth="21600" windowHeight="12585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -1269,7 +1269,7 @@
         <v>-13</v>
       </c>
       <c r="C2">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1280,7 +1280,7 @@
         <v>-3</v>
       </c>
       <c r="C3">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1288,10 +1288,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="C4">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1310,10 +1310,10 @@
         <v>0</v>
       </c>
       <c r="B6">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="C6">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1321,10 +1321,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="C7">
-        <v>-3</v>
+        <v>-8</v>
       </c>
     </row>
   </sheetData>
@@ -1333,12 +1333,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1482,6 +1476,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1492,15 +1492,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE2417C-9996-4510-9140-E726E730908D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF47025-38FC-4D4C-A172-57EF19919DA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1518,6 +1509,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE2417C-9996-4510-9140-E726E730908D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF0E423-9D38-426D-8974-49181EF85CAD}">
   <ds:schemaRefs>

--- a/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
+++ b/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\SK\eps-southkorea\InputData\trans\TTLE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\TTLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166235BA-B9A1-474C-A7BC-45EBD99E9D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2886E2FB-015D-47A1-A529-D114D3FBC4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25860" yWindow="1755" windowWidth="21600" windowHeight="12585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
-    <sheet name="TTLE" sheetId="10" r:id="rId2"/>
+    <sheet name="A54.tranSubsector_logit_revised" sheetId="11" r:id="rId2"/>
+    <sheet name="TTLE" sheetId="10" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="69">
   <si>
     <t>ships</t>
   </si>
@@ -67,9 +68,6 @@
     <t>Logit exponent</t>
   </si>
   <si>
-    <t>None needed.  Handled through calibration.</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -88,10 +86,160 @@
     <t>data on technology buyers' behavior.</t>
   </si>
   <si>
-    <t>For more on this, see the "Modified Logit" equation description at:</t>
-  </si>
-  <si>
     <t>https://jgcri.github.io/gcam-doc/choice.html</t>
+  </si>
+  <si>
+    <t># File: A54.tranSubsector_logit_revised.csv</t>
+  </si>
+  <si>
+    <t># Title: Transportation default subsector logit exponents</t>
+  </si>
+  <si>
+    <t># Source: Documented in JIRA issue https://jira.pnnl.gov/jira/browse/JGCRI-358?src=confmacro.</t>
+  </si>
+  <si>
+    <t># Units: Unitless</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Column types: ccicc </t>
+  </si>
+  <si>
+    <t># ----------</t>
+  </si>
+  <si>
+    <t>supplysector</t>
+  </si>
+  <si>
+    <t>tranSubsector</t>
+  </si>
+  <si>
+    <t>logit.exponent</t>
+  </si>
+  <si>
+    <t>logit.factor</t>
+  </si>
+  <si>
+    <t>logit.type</t>
+  </si>
+  <si>
+    <t>trn_aviation_intl</t>
+  </si>
+  <si>
+    <t>International Aviation</t>
+  </si>
+  <si>
+    <t>absolute-cost-logit</t>
+  </si>
+  <si>
+    <t>trn_freight</t>
+  </si>
+  <si>
+    <t>Domestic Ship</t>
+  </si>
+  <si>
+    <t>Freight Rail</t>
+  </si>
+  <si>
+    <t>Fuel types and efficiency levels</t>
+  </si>
+  <si>
+    <t>trn_freight_road</t>
+  </si>
+  <si>
+    <t>Light truck</t>
+  </si>
+  <si>
+    <t>Fuel types</t>
+  </si>
+  <si>
+    <t>Medium truck</t>
+  </si>
+  <si>
+    <t>Heavy truck</t>
+  </si>
+  <si>
+    <t>trn_pass</t>
+  </si>
+  <si>
+    <t>Cycle</t>
+  </si>
+  <si>
+    <t>Domestic Aviation</t>
+  </si>
+  <si>
+    <t>HSR</t>
+  </si>
+  <si>
+    <t>Passenger Rail</t>
+  </si>
+  <si>
+    <t>Walk</t>
+  </si>
+  <si>
+    <t>trn_pass_road</t>
+  </si>
+  <si>
+    <t>Bus</t>
+  </si>
+  <si>
+    <t>trn_pass_road_LDV</t>
+  </si>
+  <si>
+    <t>2W and 3W</t>
+  </si>
+  <si>
+    <t>trn_pass_road_LDV_4W</t>
+  </si>
+  <si>
+    <t>Car</t>
+  </si>
+  <si>
+    <t>Fuel types and ICE efficiency levels</t>
+  </si>
+  <si>
+    <t>Large Car and Truck</t>
+  </si>
+  <si>
+    <t>Mini Car</t>
+  </si>
+  <si>
+    <t>trn_shipping_intl</t>
+  </si>
+  <si>
+    <t>International Ship</t>
+  </si>
+  <si>
+    <t># Passthrough tranSubsectors are listed belowabsolute-cost-logit</t>
+  </si>
+  <si>
+    <t>road</t>
+  </si>
+  <si>
+    <t>LDV</t>
+  </si>
+  <si>
+    <t>bus</t>
+  </si>
+  <si>
+    <t>4W</t>
+  </si>
+  <si>
+    <t>2W</t>
+  </si>
+  <si>
+    <t>For more on this, see the "Unmodified Logit" equation description at:</t>
+  </si>
+  <si>
+    <t>PNNL</t>
+  </si>
+  <si>
+    <t>Global Change Analysis Model</t>
+  </si>
+  <si>
+    <t>https://github.com/JGCRI/gcam-core/tree/master/input/gcamdata/inst/extdata/energy</t>
+  </si>
+  <si>
+    <t>input &gt; gcamdata &gt; inst &gt; extdata &gt; energy &gt; A54.tranSubsector_logit_revised.csv</t>
   </si>
 </sst>
 </file>
@@ -1169,67 +1317,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="45.42578125" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1"/>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1238,19 +1404,438 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97FB3F6-A063-4685-A6D1-3D6F2007ED8F}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.453125" customWidth="1"/>
+    <col min="2" max="2" width="34.1796875" customWidth="1"/>
+    <col min="3" max="3" width="14.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>-6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9">
+        <v>-6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10">
+        <v>-1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11">
+        <v>-8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12">
+        <v>-8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13">
+        <v>-8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14">
+        <v>-6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15">
+        <v>-6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>-6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17">
+        <v>-1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18">
+        <v>-6</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19">
+        <v>-3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20">
+        <v>-8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21">
+        <v>-8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22">
+        <v>-8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23">
+        <v>-8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24">
+        <v>-6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26">
+        <v>-6</v>
+      </c>
+      <c r="E26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27">
+        <v>-6</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28">
+        <v>-6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29">
+        <v>-6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30">
+        <v>-6</v>
+      </c>
+      <c r="E30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31">
+        <v>-6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -1261,267 +1846,85 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>-13</v>
+        <f>'A54.tranSubsector_logit_revised'!C21</f>
+        <v>-8</v>
       </c>
       <c r="C2">
+        <f>'A54.tranSubsector_logit_revised'!C12</f>
         <v>-8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
+        <f>'A54.tranSubsector_logit_revised'!C19</f>
         <v>-3</v>
       </c>
       <c r="C3">
+        <f>'A54.tranSubsector_logit_revised'!C13</f>
         <v>-8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
+        <f>'A54.tranSubsector_logit_revised'!C15</f>
         <v>-6</v>
       </c>
       <c r="C4">
+        <f>B4</f>
         <v>-6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5">
-        <v>-0.1</v>
+        <f>'A54.tranSubsector_logit_revised'!C17</f>
+        <v>-1</v>
       </c>
       <c r="C5">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <f>'A54.tranSubsector_logit_revised'!C10</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>0</v>
       </c>
       <c r="B6">
+        <f>'A54.tranSubsector_logit_revised'!C9</f>
         <v>-6</v>
       </c>
       <c r="C6">
+        <f>'A54.tranSubsector_logit_revised'!C24</f>
         <v>-6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
+        <f>'A54.tranSubsector_logit_revised'!C20</f>
         <v>-8</v>
       </c>
       <c r="C7">
+        <f>'A54.tranSubsector_logit_revised'!C20</f>
         <v>-8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
-    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF47025-38FC-4D4C-A172-57EF19919DA6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE2417C-9996-4510-9140-E726E730908D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CF0E423-9D38-426D-8974-49181EF85CAD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
+++ b/InputData/trans/TTLE/Transportation Technology Logit Exponents.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\TTLE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-southkorea\InputData\trans\TTLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2886E2FB-015D-47A1-A529-D114D3FBC4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2599FC5E-F79F-4404-B21B-3ECA20EDA8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -1855,8 +1855,7 @@
         <v>-8</v>
       </c>
       <c r="C2">
-        <f>'A54.tranSubsector_logit_revised'!C12</f>
-        <v>-8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
